--- a/verification/cases/roundtrip/formulas_engineering/init.xlsx
+++ b/verification/cases/roundtrip/formulas_engineering/init.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/engineering/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC4D83DE-3F13-2F4A-9518-6D8F1ED032AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC001E2C-6726-4A0C-983E-393EF1D9655E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2960" yWindow="2040" windowWidth="45420" windowHeight="26100" xr2:uid="{EBAE8DC8-7645-0242-B87E-374227F9D1A2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EBAE8DC8-7645-0242-B87E-374227F9D1A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -435,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -456,19 +456,18 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -486,20 +485,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -835,7 +830,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -858,23 +853,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE264CE-503F-1742-ACB5-3ABAB7BB8E79}">
   <dimension ref="B2:M117"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="12" t="s">
         <v>0</v>
       </c>
@@ -887,28 +882,26 @@
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="14" t="s">
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="15">
-        <v>0</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
@@ -924,7 +917,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
@@ -940,7 +933,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
@@ -956,7 +949,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
@@ -972,7 +965,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
@@ -988,7 +981,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
@@ -1004,7 +997,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1020,7 +1013,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
@@ -1036,7 +1029,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
@@ -1052,7 +1045,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
@@ -1068,8 +1061,8 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="17" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
+    <row r="17" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="3"/>
@@ -1084,90 +1077,90 @@
       <c r="L17" s="3"/>
       <c r="M17" s="12"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B18" s="19" t="s">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B18" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="29" t="s">
+      <c r="H18" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="I18" s="29" t="s">
+      <c r="I18" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="29" t="s">
+      <c r="J18" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="29" t="s">
+      <c r="L18" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="M18" s="34"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B19" s="21">
+      <c r="M18" s="31"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B19" s="20">
         <f>$C$5</f>
         <v>0</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="25">
         <f>IFERROR(CONVERT($C$5,"lbm","kg"),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="25">
         <f>IFERROR(CONVERT($C$5,"mi","km"),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="25">
         <f>IFERROR(CONVERT($C$5,"ft","m"),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="25">
         <f>IFERROR(CONVERT($C$5,"gal","l"),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="25">
         <f>IFERROR(CONVERT($C$5,"F","C"),"N/A")</f>
         <v>-17.777777777777779</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="25">
         <f>IFERROR(CONVERT($C$5,"C","K"),"N/A")</f>
         <v>273.14999999999998</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="25">
         <f>IFERROR(CONVERT($C$5,"hr","mn"),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="25">
         <f>IFERROR(CONVERT($C$5,"in","cm"),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="K19" s="26">
+      <c r="K19" s="25">
         <f>IFERROR(CONVERT($C$5,"yd","m"),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="L19" s="26" t="str">
+      <c r="L19" s="25" t="str">
         <f>IFERROR(CONVERT($C$5,"oz","g"),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="M19" s="33"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M19" s="8"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="6">
         <f>$C$6</f>
         <v>1</v>
@@ -1214,7 +1207,7 @@
       </c>
       <c r="M20" s="8"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="6">
         <f>$C$7</f>
         <v>-1</v>
@@ -1261,7 +1254,7 @@
       </c>
       <c r="M21" s="8"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="6">
         <f>$C$8</f>
         <v>10</v>
@@ -1308,7 +1301,7 @@
       </c>
       <c r="M22" s="8"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="6">
         <f>$C$9</f>
         <v>-10</v>
@@ -1355,7 +1348,7 @@
       </c>
       <c r="M23" s="8"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="6">
         <f>$C$10</f>
         <v>511</v>
@@ -1402,7 +1395,7 @@
       </c>
       <c r="M24" s="8"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="6">
         <f>$C$11</f>
         <v>-512</v>
@@ -1449,7 +1442,7 @@
       </c>
       <c r="M25" s="8"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="6">
         <f>$C$12</f>
         <v>255</v>
@@ -1496,7 +1489,7 @@
       </c>
       <c r="M26" s="8"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="6">
         <f>$C$13</f>
         <v>-255</v>
@@ -1543,7 +1536,7 @@
       </c>
       <c r="M27" s="8"/>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="6">
         <f>$C$14</f>
         <v>42.5</v>
@@ -1590,7 +1583,7 @@
       </c>
       <c r="M28" s="8"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="6">
         <f>$C$15</f>
         <v>-42.5</v>
@@ -1637,7 +1630,7 @@
       </c>
       <c r="M29" s="8"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
@@ -1649,8 +1642,8 @@
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
     </row>
-    <row r="31" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="18" t="s">
+    <row r="31" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="17" t="s">
         <v>26</v>
       </c>
       <c r="C31" s="3"/>
@@ -1665,65 +1658,65 @@
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B32" s="19" t="s">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="29">
         <v>4</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="29">
         <v>6</v>
       </c>
-      <c r="F32" s="31">
+      <c r="F32" s="29">
         <v>8</v>
       </c>
-      <c r="G32" s="31">
+      <c r="G32" s="29">
         <v>10</v>
       </c>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B33" s="21">
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B33" s="20">
         <f>$C$5</f>
         <v>0</v>
       </c>
-      <c r="C33" s="26" t="str">
+      <c r="C33" s="25" t="str">
         <f>IFERROR(DEC2BIN($C$5),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="26" t="str">
+      <c r="D33" s="25" t="str">
         <f>IFERROR(DEC2BIN($C$5,4),"N/A")</f>
         <v>0000</v>
       </c>
-      <c r="E33" s="26" t="str">
+      <c r="E33" s="25" t="str">
         <f>IFERROR(DEC2BIN($C$5,6),"N/A")</f>
         <v>000000</v>
       </c>
-      <c r="F33" s="26" t="str">
+      <c r="F33" s="25" t="str">
         <f>IFERROR(DEC2BIN($C$5,8),"N/A")</f>
         <v>00000000</v>
       </c>
-      <c r="G33" s="26" t="str">
+      <c r="G33" s="25" t="str">
         <f>IFERROR(DEC2BIN($C$5,10),"N/A")</f>
         <v>0000000000</v>
       </c>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="33"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="8"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="6">
         <f>$C$6</f>
         <v>1</v>
@@ -1755,7 +1748,7 @@
       <c r="L34" s="8"/>
       <c r="M34" s="8"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="6">
         <f>$C$7</f>
         <v>-1</v>
@@ -1787,7 +1780,7 @@
       <c r="L35" s="8"/>
       <c r="M35" s="8"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="6">
         <f>$C$8</f>
         <v>10</v>
@@ -1819,7 +1812,7 @@
       <c r="L36" s="8"/>
       <c r="M36" s="8"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="6">
         <f>$C$9</f>
         <v>-10</v>
@@ -1851,7 +1844,7 @@
       <c r="L37" s="8"/>
       <c r="M37" s="8"/>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="6">
         <f>$C$10</f>
         <v>511</v>
@@ -1883,7 +1876,7 @@
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="6">
         <f>$C$11</f>
         <v>-512</v>
@@ -1915,7 +1908,7 @@
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="6">
         <f>$C$12</f>
         <v>255</v>
@@ -1947,7 +1940,7 @@
       <c r="L40" s="8"/>
       <c r="M40" s="8"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="6">
         <f>$C$13</f>
         <v>-255</v>
@@ -1979,7 +1972,7 @@
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
@@ -1992,8 +1985,8 @@
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
     </row>
-    <row r="43" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="18" t="s">
+    <row r="43" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="17" t="s">
         <v>29</v>
       </c>
       <c r="C43" s="3"/>
@@ -2008,70 +2001,70 @@
       <c r="L43" s="12"/>
       <c r="M43" s="8"/>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B44" s="19" t="s">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B44" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C44" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="29">
         <v>2</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="29">
         <v>4</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="29">
         <v>6</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="29">
         <v>8</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="29">
         <v>10</v>
       </c>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="34"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B45" s="21">
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B45" s="20">
         <f>$C$5</f>
         <v>0</v>
       </c>
-      <c r="C45" s="26" t="str">
+      <c r="C45" s="25" t="str">
         <f>IFERROR(DEC2HEX($C$5),"N/A")</f>
         <v>0</v>
       </c>
-      <c r="D45" s="26" t="str">
+      <c r="D45" s="25" t="str">
         <f>IFERROR(DEC2HEX($C$5,2),"N/A")</f>
         <v>00</v>
       </c>
-      <c r="E45" s="26" t="str">
+      <c r="E45" s="25" t="str">
         <f>IFERROR(DEC2HEX($C$5,4),"N/A")</f>
         <v>0000</v>
       </c>
-      <c r="F45" s="26" t="str">
+      <c r="F45" s="25" t="str">
         <f>IFERROR(DEC2HEX($C$5,6),"N/A")</f>
         <v>000000</v>
       </c>
-      <c r="G45" s="26" t="str">
+      <c r="G45" s="25" t="str">
         <f>IFERROR(DEC2HEX($C$5,8),"N/A")</f>
         <v>00000000</v>
       </c>
-      <c r="H45" s="26" t="str">
+      <c r="H45" s="25" t="str">
         <f>IFERROR(DEC2HEX($C$5,10),"N/A")</f>
         <v>0000000000</v>
       </c>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="33"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="31"/>
+      <c r="M45" s="8"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="6">
         <f>$C$6</f>
         <v>1</v>
@@ -2106,7 +2099,7 @@
       <c r="L46" s="8"/>
       <c r="M46" s="8"/>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="6">
         <f>$C$7</f>
         <v>-1</v>
@@ -2141,7 +2134,7 @@
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B48" s="6">
         <f>$C$8</f>
         <v>10</v>
@@ -2176,7 +2169,7 @@
       <c r="L48" s="8"/>
       <c r="M48" s="8"/>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B49" s="6">
         <f>$C$9</f>
         <v>-10</v>
@@ -2211,7 +2204,7 @@
       <c r="L49" s="8"/>
       <c r="M49" s="8"/>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B50" s="6">
         <f>$C$10</f>
         <v>511</v>
@@ -2246,7 +2239,7 @@
       <c r="L50" s="8"/>
       <c r="M50" s="8"/>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B51" s="6">
         <f>$C$11</f>
         <v>-512</v>
@@ -2281,7 +2274,7 @@
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B52" s="6">
         <f>$C$12</f>
         <v>255</v>
@@ -2316,7 +2309,7 @@
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B53" s="6">
         <f>$C$13</f>
         <v>-255</v>
@@ -2351,7 +2344,7 @@
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B54" s="6">
         <f>$C$14</f>
         <v>42.5</v>
@@ -2386,7 +2379,7 @@
       <c r="L54" s="8"/>
       <c r="M54" s="8"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B55" s="6">
         <f>$C$15</f>
         <v>-42.5</v>
@@ -2421,7 +2414,7 @@
       <c r="L55" s="8"/>
       <c r="M55" s="8"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
@@ -2434,70 +2427,70 @@
       <c r="L56" s="8"/>
       <c r="M56" s="8"/>
     </row>
-    <row r="57" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="18" t="s">
+    <row r="57" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="17" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-      <c r="J57" s="22"/>
-      <c r="K57" s="22"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="21"/>
       <c r="L57" s="12"/>
       <c r="M57" s="8"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B58" s="20" t="s">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B58" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="30" t="s">
+      <c r="C58" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D58" s="30"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34"/>
-      <c r="I58" s="34"/>
-      <c r="J58" s="34"/>
-      <c r="K58" s="34"/>
-      <c r="L58" s="34"/>
-      <c r="M58" s="34"/>
-    </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B59" s="23" t="s">
+      <c r="D58" s="9"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B59" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="26">
-        <f>IFERROR(BIN2DEC(B59),"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="D59" s="27" t="s">
+      <c r="C59" s="25">
+        <f t="shared" ref="C59:C69" si="0">IFERROR(BIN2DEC(B59),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
-      <c r="H59" s="34"/>
-      <c r="I59" s="34"/>
-      <c r="J59" s="34"/>
-      <c r="K59" s="34"/>
-      <c r="L59" s="34"/>
-      <c r="M59" s="33"/>
-    </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="31"/>
+      <c r="I59" s="31"/>
+      <c r="J59" s="31"/>
+      <c r="K59" s="31"/>
+      <c r="L59" s="31"/>
+      <c r="M59" s="8"/>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B60" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="7">
-        <f>IFERROR(BIN2DEC(B60),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="26" t="s">
         <v>34</v>
       </c>
       <c r="E60" s="8"/>
@@ -2510,15 +2503,15 @@
       <c r="L60" s="8"/>
       <c r="M60" s="8"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B61" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="7">
-        <f>IFERROR(BIN2DEC(B61),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="26" t="s">
         <v>35</v>
       </c>
       <c r="E61" s="8"/>
@@ -2531,15 +2524,15 @@
       <c r="L61" s="8"/>
       <c r="M61" s="8"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B62" s="11" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="7">
-        <f>IFERROR(BIN2DEC(B62),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="26" t="s">
         <v>36</v>
       </c>
       <c r="E62" s="8"/>
@@ -2552,15 +2545,15 @@
       <c r="L62" s="8"/>
       <c r="M62" s="8"/>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B63" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C63" s="7">
-        <f>IFERROR(BIN2DEC(B63),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="D63" s="27" t="s">
+      <c r="D63" s="26" t="s">
         <v>37</v>
       </c>
       <c r="E63" s="8"/>
@@ -2573,15 +2566,15 @@
       <c r="L63" s="8"/>
       <c r="M63" s="8"/>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B64" s="11" t="s">
         <v>69</v>
       </c>
       <c r="C64" s="7">
-        <f>IFERROR(BIN2DEC(B64),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>255</v>
       </c>
-      <c r="D64" s="27" t="s">
+      <c r="D64" s="26" t="s">
         <v>38</v>
       </c>
       <c r="E64" s="8"/>
@@ -2594,15 +2587,15 @@
       <c r="L64" s="8"/>
       <c r="M64" s="8"/>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" s="11" t="s">
         <v>70</v>
       </c>
       <c r="C65" s="7">
-        <f>IFERROR(BIN2DEC(B65),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>511</v>
       </c>
-      <c r="D65" s="27" t="s">
+      <c r="D65" s="26" t="s">
         <v>39</v>
       </c>
       <c r="E65" s="8"/>
@@ -2615,15 +2608,15 @@
       <c r="L65" s="8"/>
       <c r="M65" s="8"/>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66" s="11" t="s">
         <v>71</v>
       </c>
       <c r="C66" s="7">
-        <f>IFERROR(BIN2DEC(B66),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>-512</v>
       </c>
-      <c r="D66" s="27" t="s">
+      <c r="D66" s="26" t="s">
         <v>40</v>
       </c>
       <c r="E66" s="8"/>
@@ -2636,15 +2629,15 @@
       <c r="L66" s="8"/>
       <c r="M66" s="8"/>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B67" s="11" t="s">
         <v>72</v>
       </c>
       <c r="C67" s="7">
-        <f>IFERROR(BIN2DEC(B67),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="D67" s="27" t="s">
+      <c r="D67" s="26" t="s">
         <v>41</v>
       </c>
       <c r="E67" s="8"/>
@@ -2657,15 +2650,15 @@
       <c r="L67" s="8"/>
       <c r="M67" s="8"/>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="11" t="s">
         <v>73</v>
       </c>
       <c r="C68" s="7">
-        <f>IFERROR(BIN2DEC(B68),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D68" s="27" t="s">
+      <c r="D68" s="26" t="s">
         <v>42</v>
       </c>
       <c r="E68" s="8"/>
@@ -2678,15 +2671,15 @@
       <c r="L68" s="8"/>
       <c r="M68" s="8"/>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C69" s="7">
-        <f>IFERROR(BIN2DEC(B69),"N/A")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="26" t="s">
         <v>43</v>
       </c>
       <c r="E69" s="8"/>
@@ -2699,7 +2692,7 @@
       <c r="L69" s="8"/>
       <c r="M69" s="8"/>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="8"/>
@@ -2712,70 +2705,70 @@
       <c r="L70" s="8"/>
       <c r="M70" s="8"/>
     </row>
-    <row r="71" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="18" t="s">
+    <row r="71" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
       <c r="L71" s="12"/>
       <c r="M71" s="8"/>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B72" s="20" t="s">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B72" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C72" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D72" s="30"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="34"/>
-      <c r="H72" s="34"/>
-      <c r="I72" s="34"/>
-      <c r="J72" s="34"/>
-      <c r="K72" s="34"/>
-      <c r="L72" s="34"/>
-      <c r="M72" s="34"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B73" s="24">
-        <v>0</v>
-      </c>
-      <c r="C73" s="26">
-        <f>IFERROR(HEX2DEC(B73),"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="27" t="s">
+      <c r="D72" s="9"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+      <c r="J72" s="31"/>
+      <c r="K72" s="31"/>
+      <c r="L72" s="31"/>
+      <c r="M72" s="31"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B73" s="23">
+        <v>0</v>
+      </c>
+      <c r="C73" s="25">
+        <f t="shared" ref="C73:C83" si="1">IFERROR(HEX2DEC(B73),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E73" s="34"/>
-      <c r="F73" s="34"/>
-      <c r="G73" s="34"/>
-      <c r="H73" s="34"/>
-      <c r="I73" s="34"/>
-      <c r="J73" s="34"/>
-      <c r="K73" s="34"/>
-      <c r="L73" s="34"/>
-      <c r="M73" s="33"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E73" s="31"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="31"/>
+      <c r="I73" s="31"/>
+      <c r="J73" s="31"/>
+      <c r="K73" s="31"/>
+      <c r="L73" s="31"/>
+      <c r="M73" s="8"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B74" s="10">
         <v>1</v>
       </c>
       <c r="C74" s="7">
-        <f>IFERROR(HEX2DEC(B74),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="D74" s="27" t="s">
+      <c r="D74" s="26" t="s">
         <v>34</v>
       </c>
       <c r="E74" s="8"/>
@@ -2788,15 +2781,15 @@
       <c r="L74" s="8"/>
       <c r="M74" s="8"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C75" s="7">
-        <f>IFERROR(HEX2DEC(B75),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="D75" s="27" t="s">
+      <c r="D75" s="26" t="s">
         <v>47</v>
       </c>
       <c r="E75" s="8"/>
@@ -2809,15 +2802,15 @@
       <c r="L75" s="8"/>
       <c r="M75" s="8"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B76" s="10" t="s">
         <v>48</v>
       </c>
       <c r="C76" s="7">
-        <f>IFERROR(HEX2DEC(B76),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="D76" s="27" t="s">
+      <c r="D76" s="26" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="8"/>
@@ -2830,15 +2823,15 @@
       <c r="L76" s="8"/>
       <c r="M76" s="8"/>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B77" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C77" s="7">
-        <f>IFERROR(HEX2DEC(B77),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>255</v>
       </c>
-      <c r="D77" s="27" t="s">
+      <c r="D77" s="26" t="s">
         <v>51</v>
       </c>
       <c r="E77" s="8"/>
@@ -2851,15 +2844,15 @@
       <c r="L77" s="8"/>
       <c r="M77" s="8"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C78" s="7">
-        <f>IFERROR(HEX2DEC(B78),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>511</v>
       </c>
-      <c r="D78" s="27" t="s">
+      <c r="D78" s="26" t="s">
         <v>53</v>
       </c>
       <c r="E78" s="8"/>
@@ -2872,15 +2865,15 @@
       <c r="L78" s="8"/>
       <c r="M78" s="8"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B79" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C79" s="7">
-        <f>IFERROR(HEX2DEC(B79),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="D79" s="27" t="s">
+      <c r="D79" s="26" t="s">
         <v>55</v>
       </c>
       <c r="E79" s="8"/>
@@ -2893,15 +2886,15 @@
       <c r="L79" s="8"/>
       <c r="M79" s="8"/>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B80" s="10" t="s">
         <v>56</v>
       </c>
       <c r="C80" s="7">
-        <f>IFERROR(HEX2DEC(B80),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>-512</v>
       </c>
-      <c r="D80" s="27" t="s">
+      <c r="D80" s="26" t="s">
         <v>57</v>
       </c>
       <c r="E80" s="8"/>
@@ -2914,15 +2907,15 @@
       <c r="L80" s="8"/>
       <c r="M80" s="8"/>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B81" s="10" t="s">
         <v>58</v>
       </c>
       <c r="C81" s="7">
-        <f>IFERROR(HEX2DEC(B81),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="D81" s="27" t="s">
+      <c r="D81" s="26" t="s">
         <v>59</v>
       </c>
       <c r="E81" s="8"/>
@@ -2935,15 +2928,15 @@
       <c r="L81" s="8"/>
       <c r="M81" s="8"/>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B82" s="10" t="s">
         <v>60</v>
       </c>
       <c r="C82" s="7">
-        <f>IFERROR(HEX2DEC(B82),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>-42</v>
       </c>
-      <c r="D82" s="27" t="s">
+      <c r="D82" s="26" t="s">
         <v>61</v>
       </c>
       <c r="E82" s="8"/>
@@ -2956,15 +2949,15 @@
       <c r="L82" s="8"/>
       <c r="M82" s="8"/>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B83" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C83" s="7">
-        <f>IFERROR(HEX2DEC(B83),"N/A")</f>
+        <f t="shared" si="1"/>
         <v>549755813887</v>
       </c>
-      <c r="D83" s="27" t="s">
+      <c r="D83" s="26" t="s">
         <v>63</v>
       </c>
       <c r="E83" s="8"/>
@@ -2977,7 +2970,7 @@
       <c r="L83" s="8"/>
       <c r="M83" s="8"/>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
       <c r="E84" s="8"/>
@@ -2990,8 +2983,8 @@
       <c r="L84" s="8"/>
       <c r="M84" s="8"/>
     </row>
-    <row r="85" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="28" t="s">
+    <row r="85" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="27" t="s">
         <v>75</v>
       </c>
       <c r="C85" s="3"/>
@@ -3006,103 +2999,103 @@
       <c r="L85" s="12"/>
       <c r="M85" s="8"/>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B86" s="25" t="s">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B86" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C86" s="32">
-        <v>0</v>
-      </c>
-      <c r="D86" s="32">
+      <c r="C86" s="30">
+        <v>0</v>
+      </c>
+      <c r="D86" s="30">
         <v>1</v>
       </c>
-      <c r="E86" s="32">
+      <c r="E86" s="30">
         <v>-1</v>
       </c>
-      <c r="F86" s="32">
+      <c r="F86" s="30">
         <v>5</v>
       </c>
-      <c r="G86" s="32">
+      <c r="G86" s="30">
         <v>-5</v>
       </c>
-      <c r="H86" s="32">
+      <c r="H86" s="30">
         <v>0.5</v>
       </c>
-      <c r="I86" s="32">
+      <c r="I86" s="30">
         <v>-0.5</v>
       </c>
-      <c r="J86" s="34"/>
-      <c r="K86" s="34"/>
-      <c r="L86" s="34"/>
-      <c r="M86" s="34"/>
-    </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B87" s="21">
-        <v>0</v>
-      </c>
-      <c r="C87" s="26" t="str">
-        <f>IFERROR(COMPLEX($B87,C$86),"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="D87" s="26" t="str">
-        <f>IFERROR(COMPLEX($B87,D$86),"N/A")</f>
+      <c r="J86" s="31"/>
+      <c r="K86" s="31"/>
+      <c r="L86" s="31"/>
+      <c r="M86" s="31"/>
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B87" s="20">
+        <v>0</v>
+      </c>
+      <c r="C87" s="25" t="str">
+        <f t="shared" ref="C87:I93" si="2">IFERROR(COMPLEX($B87,C$86),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D87" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>i</v>
       </c>
-      <c r="E87" s="26" t="str">
-        <f>IFERROR(COMPLEX($B87,E$86),"N/A")</f>
+      <c r="E87" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>-i</v>
       </c>
-      <c r="F87" s="26" t="str">
-        <f>IFERROR(COMPLEX($B87,F$86),"N/A")</f>
+      <c r="F87" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>5i</v>
       </c>
-      <c r="G87" s="26" t="str">
-        <f>IFERROR(COMPLEX($B87,G$86),"N/A")</f>
+      <c r="G87" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>-5i</v>
       </c>
-      <c r="H87" s="26" t="str">
-        <f>IFERROR(COMPLEX($B87,H$86),"N/A")</f>
+      <c r="H87" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>0.5i</v>
       </c>
-      <c r="I87" s="26" t="str">
-        <f>IFERROR(COMPLEX($B87,I$86),"N/A")</f>
+      <c r="I87" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>-0.5i</v>
       </c>
-      <c r="J87" s="34"/>
-      <c r="K87" s="34"/>
-      <c r="L87" s="34"/>
-      <c r="M87" s="33"/>
-    </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="J87" s="31"/>
+      <c r="K87" s="31"/>
+      <c r="L87" s="31"/>
+      <c r="M87" s="8"/>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B88" s="6">
         <v>1</v>
       </c>
       <c r="C88" s="7" t="str">
-        <f>IFERROR(COMPLEX($B88,C$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D88" s="7" t="str">
-        <f>IFERROR(COMPLEX($B88,D$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>1+i</v>
       </c>
       <c r="E88" s="7" t="str">
-        <f>IFERROR(COMPLEX($B88,E$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>1-i</v>
       </c>
       <c r="F88" s="7" t="str">
-        <f>IFERROR(COMPLEX($B88,F$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>1+5i</v>
       </c>
       <c r="G88" s="7" t="str">
-        <f>IFERROR(COMPLEX($B88,G$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>1-5i</v>
       </c>
       <c r="H88" s="7" t="str">
-        <f>IFERROR(COMPLEX($B88,H$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>1+0.5i</v>
       </c>
       <c r="I88" s="7" t="str">
-        <f>IFERROR(COMPLEX($B88,I$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>1-0.5i</v>
       </c>
       <c r="J88" s="8"/>
@@ -3110,36 +3103,36 @@
       <c r="L88" s="8"/>
       <c r="M88" s="8"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B89" s="6">
         <v>-1</v>
       </c>
       <c r="C89" s="7" t="str">
-        <f>IFERROR(COMPLEX($B89,C$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="D89" s="7" t="str">
-        <f>IFERROR(COMPLEX($B89,D$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-1+i</v>
       </c>
       <c r="E89" s="7" t="str">
-        <f>IFERROR(COMPLEX($B89,E$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-1-i</v>
       </c>
       <c r="F89" s="7" t="str">
-        <f>IFERROR(COMPLEX($B89,F$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-1+5i</v>
       </c>
       <c r="G89" s="7" t="str">
-        <f>IFERROR(COMPLEX($B89,G$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-1-5i</v>
       </c>
       <c r="H89" s="7" t="str">
-        <f>IFERROR(COMPLEX($B89,H$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-1+0.5i</v>
       </c>
       <c r="I89" s="7" t="str">
-        <f>IFERROR(COMPLEX($B89,I$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-1-0.5i</v>
       </c>
       <c r="J89" s="8"/>
@@ -3147,36 +3140,36 @@
       <c r="L89" s="8"/>
       <c r="M89" s="8"/>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B90" s="6">
         <v>5</v>
       </c>
       <c r="C90" s="7" t="str">
-        <f>IFERROR(COMPLEX($B90,C$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="D90" s="7" t="str">
-        <f>IFERROR(COMPLEX($B90,D$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>5+i</v>
       </c>
       <c r="E90" s="7" t="str">
-        <f>IFERROR(COMPLEX($B90,E$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>5-i</v>
       </c>
       <c r="F90" s="7" t="str">
-        <f>IFERROR(COMPLEX($B90,F$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>5+5i</v>
       </c>
       <c r="G90" s="7" t="str">
-        <f>IFERROR(COMPLEX($B90,G$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>5-5i</v>
       </c>
       <c r="H90" s="7" t="str">
-        <f>IFERROR(COMPLEX($B90,H$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>5+0.5i</v>
       </c>
       <c r="I90" s="7" t="str">
-        <f>IFERROR(COMPLEX($B90,I$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>5-0.5i</v>
       </c>
       <c r="J90" s="8"/>
@@ -3184,36 +3177,36 @@
       <c r="L90" s="8"/>
       <c r="M90" s="8"/>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B91" s="6">
         <v>-5</v>
       </c>
       <c r="C91" s="7" t="str">
-        <f>IFERROR(COMPLEX($B91,C$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-5</v>
       </c>
       <c r="D91" s="7" t="str">
-        <f>IFERROR(COMPLEX($B91,D$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-5+i</v>
       </c>
       <c r="E91" s="7" t="str">
-        <f>IFERROR(COMPLEX($B91,E$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-5-i</v>
       </c>
       <c r="F91" s="7" t="str">
-        <f>IFERROR(COMPLEX($B91,F$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-5+5i</v>
       </c>
       <c r="G91" s="7" t="str">
-        <f>IFERROR(COMPLEX($B91,G$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-5-5i</v>
       </c>
       <c r="H91" s="7" t="str">
-        <f>IFERROR(COMPLEX($B91,H$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-5+0.5i</v>
       </c>
       <c r="I91" s="7" t="str">
-        <f>IFERROR(COMPLEX($B91,I$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-5-0.5i</v>
       </c>
       <c r="J91" s="8"/>
@@ -3221,36 +3214,36 @@
       <c r="L91" s="8"/>
       <c r="M91" s="8"/>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B92" s="6">
         <v>0.5</v>
       </c>
       <c r="C92" s="7" t="str">
-        <f>IFERROR(COMPLEX($B92,C$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="D92" s="7" t="str">
-        <f>IFERROR(COMPLEX($B92,D$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>0.5+i</v>
       </c>
       <c r="E92" s="7" t="str">
-        <f>IFERROR(COMPLEX($B92,E$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>0.5-i</v>
       </c>
       <c r="F92" s="7" t="str">
-        <f>IFERROR(COMPLEX($B92,F$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>0.5+5i</v>
       </c>
       <c r="G92" s="7" t="str">
-        <f>IFERROR(COMPLEX($B92,G$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>0.5-5i</v>
       </c>
       <c r="H92" s="7" t="str">
-        <f>IFERROR(COMPLEX($B92,H$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>0.5+0.5i</v>
       </c>
       <c r="I92" s="7" t="str">
-        <f>IFERROR(COMPLEX($B92,I$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>0.5-0.5i</v>
       </c>
       <c r="J92" s="8"/>
@@ -3258,36 +3251,36 @@
       <c r="L92" s="8"/>
       <c r="M92" s="8"/>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B93" s="6">
         <v>-0.5</v>
       </c>
       <c r="C93" s="7" t="str">
-        <f>IFERROR(COMPLEX($B93,C$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="D93" s="7" t="str">
-        <f>IFERROR(COMPLEX($B93,D$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-0.5+i</v>
       </c>
       <c r="E93" s="7" t="str">
-        <f>IFERROR(COMPLEX($B93,E$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-0.5-i</v>
       </c>
       <c r="F93" s="7" t="str">
-        <f>IFERROR(COMPLEX($B93,F$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-0.5+5i</v>
       </c>
       <c r="G93" s="7" t="str">
-        <f>IFERROR(COMPLEX($B93,G$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-0.5-5i</v>
       </c>
       <c r="H93" s="7" t="str">
-        <f>IFERROR(COMPLEX($B93,H$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-0.5+0.5i</v>
       </c>
       <c r="I93" s="7" t="str">
-        <f>IFERROR(COMPLEX($B93,I$86),"N/A")</f>
+        <f t="shared" si="2"/>
         <v>-0.5-0.5i</v>
       </c>
       <c r="J93" s="8"/>
@@ -3295,7 +3288,7 @@
       <c r="L93" s="8"/>
       <c r="M93" s="8"/>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
       <c r="E94" s="9"/>
@@ -3308,8 +3301,8 @@
       <c r="L94" s="8"/>
       <c r="M94" s="8"/>
     </row>
-    <row r="95" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="18" t="s">
+    <row r="95" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B95" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C95" s="3"/>
@@ -3324,103 +3317,103 @@
       <c r="L95" s="12"/>
       <c r="M95" s="8"/>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B96" s="19" t="s">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B96" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C96" s="32">
-        <v>0</v>
-      </c>
-      <c r="D96" s="32">
+      <c r="C96" s="30">
+        <v>0</v>
+      </c>
+      <c r="D96" s="30">
         <v>1</v>
       </c>
-      <c r="E96" s="32">
+      <c r="E96" s="30">
         <v>-1</v>
       </c>
-      <c r="F96" s="32">
+      <c r="F96" s="30">
         <v>5</v>
       </c>
-      <c r="G96" s="32">
+      <c r="G96" s="30">
         <v>-5</v>
       </c>
-      <c r="H96" s="32">
+      <c r="H96" s="30">
         <v>0.5</v>
       </c>
-      <c r="I96" s="32">
+      <c r="I96" s="30">
         <v>-0.5</v>
       </c>
-      <c r="J96" s="34"/>
-      <c r="K96" s="34"/>
-      <c r="L96" s="34"/>
-      <c r="M96" s="34"/>
-    </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B97" s="21">
-        <v>0</v>
-      </c>
-      <c r="C97" s="26" t="str">
-        <f>IFERROR(COMPLEX($B97,C$96,"j"),"N/A")</f>
-        <v>0</v>
-      </c>
-      <c r="D97" s="26" t="str">
-        <f>IFERROR(COMPLEX($B97,D$96,"j"),"N/A")</f>
+      <c r="J96" s="31"/>
+      <c r="K96" s="31"/>
+      <c r="L96" s="31"/>
+      <c r="M96" s="31"/>
+    </row>
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B97" s="20">
+        <v>0</v>
+      </c>
+      <c r="C97" s="25" t="str">
+        <f t="shared" ref="C97:I103" si="3">IFERROR(COMPLEX($B97,C$96,"j"),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D97" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>j</v>
       </c>
-      <c r="E97" s="26" t="str">
-        <f>IFERROR(COMPLEX($B97,E$96,"j"),"N/A")</f>
+      <c r="E97" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>-j</v>
       </c>
-      <c r="F97" s="26" t="str">
-        <f>IFERROR(COMPLEX($B97,F$96,"j"),"N/A")</f>
+      <c r="F97" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>5j</v>
       </c>
-      <c r="G97" s="26" t="str">
-        <f>IFERROR(COMPLEX($B97,G$96,"j"),"N/A")</f>
+      <c r="G97" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>-5j</v>
       </c>
-      <c r="H97" s="26" t="str">
-        <f>IFERROR(COMPLEX($B97,H$96,"j"),"N/A")</f>
+      <c r="H97" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>0.5j</v>
       </c>
-      <c r="I97" s="26" t="str">
-        <f>IFERROR(COMPLEX($B97,I$96,"j"),"N/A")</f>
+      <c r="I97" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>-0.5j</v>
       </c>
-      <c r="J97" s="34"/>
-      <c r="K97" s="34"/>
-      <c r="L97" s="34"/>
-      <c r="M97" s="33"/>
-    </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="J97" s="31"/>
+      <c r="K97" s="31"/>
+      <c r="L97" s="31"/>
+      <c r="M97" s="8"/>
+    </row>
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B98" s="6">
         <v>1</v>
       </c>
       <c r="C98" s="7" t="str">
-        <f>IFERROR(COMPLEX($B98,C$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D98" s="7" t="str">
-        <f>IFERROR(COMPLEX($B98,D$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>1+j</v>
       </c>
       <c r="E98" s="7" t="str">
-        <f>IFERROR(COMPLEX($B98,E$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>1-j</v>
       </c>
       <c r="F98" s="7" t="str">
-        <f>IFERROR(COMPLEX($B98,F$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>1+5j</v>
       </c>
       <c r="G98" s="7" t="str">
-        <f>IFERROR(COMPLEX($B98,G$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>1-5j</v>
       </c>
       <c r="H98" s="7" t="str">
-        <f>IFERROR(COMPLEX($B98,H$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>1+0.5j</v>
       </c>
       <c r="I98" s="7" t="str">
-        <f>IFERROR(COMPLEX($B98,I$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>1-0.5j</v>
       </c>
       <c r="J98" s="8"/>
@@ -3428,36 +3421,36 @@
       <c r="L98" s="8"/>
       <c r="M98" s="8"/>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B99" s="6">
         <v>-1</v>
       </c>
       <c r="C99" s="7" t="str">
-        <f>IFERROR(COMPLEX($B99,C$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="D99" s="7" t="str">
-        <f>IFERROR(COMPLEX($B99,D$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-1+j</v>
       </c>
       <c r="E99" s="7" t="str">
-        <f>IFERROR(COMPLEX($B99,E$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-1-j</v>
       </c>
       <c r="F99" s="7" t="str">
-        <f>IFERROR(COMPLEX($B99,F$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-1+5j</v>
       </c>
       <c r="G99" s="7" t="str">
-        <f>IFERROR(COMPLEX($B99,G$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-1-5j</v>
       </c>
       <c r="H99" s="7" t="str">
-        <f>IFERROR(COMPLEX($B99,H$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-1+0.5j</v>
       </c>
       <c r="I99" s="7" t="str">
-        <f>IFERROR(COMPLEX($B99,I$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-1-0.5j</v>
       </c>
       <c r="J99" s="8"/>
@@ -3465,36 +3458,36 @@
       <c r="L99" s="8"/>
       <c r="M99" s="8"/>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B100" s="6">
         <v>5</v>
       </c>
       <c r="C100" s="7" t="str">
-        <f>IFERROR(COMPLEX($B100,C$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="D100" s="7" t="str">
-        <f>IFERROR(COMPLEX($B100,D$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>5+j</v>
       </c>
       <c r="E100" s="7" t="str">
-        <f>IFERROR(COMPLEX($B100,E$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>5-j</v>
       </c>
       <c r="F100" s="7" t="str">
-        <f>IFERROR(COMPLEX($B100,F$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>5+5j</v>
       </c>
       <c r="G100" s="7" t="str">
-        <f>IFERROR(COMPLEX($B100,G$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>5-5j</v>
       </c>
       <c r="H100" s="7" t="str">
-        <f>IFERROR(COMPLEX($B100,H$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>5+0.5j</v>
       </c>
       <c r="I100" s="7" t="str">
-        <f>IFERROR(COMPLEX($B100,I$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>5-0.5j</v>
       </c>
       <c r="J100" s="8"/>
@@ -3502,36 +3495,36 @@
       <c r="L100" s="8"/>
       <c r="M100" s="8"/>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B101" s="6">
         <v>-5</v>
       </c>
       <c r="C101" s="7" t="str">
-        <f>IFERROR(COMPLEX($B101,C$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-5</v>
       </c>
       <c r="D101" s="7" t="str">
-        <f>IFERROR(COMPLEX($B101,D$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-5+j</v>
       </c>
       <c r="E101" s="7" t="str">
-        <f>IFERROR(COMPLEX($B101,E$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-5-j</v>
       </c>
       <c r="F101" s="7" t="str">
-        <f>IFERROR(COMPLEX($B101,F$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-5+5j</v>
       </c>
       <c r="G101" s="7" t="str">
-        <f>IFERROR(COMPLEX($B101,G$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-5-5j</v>
       </c>
       <c r="H101" s="7" t="str">
-        <f>IFERROR(COMPLEX($B101,H$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-5+0.5j</v>
       </c>
       <c r="I101" s="7" t="str">
-        <f>IFERROR(COMPLEX($B101,I$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-5-0.5j</v>
       </c>
       <c r="J101" s="8"/>
@@ -3539,36 +3532,36 @@
       <c r="L101" s="8"/>
       <c r="M101" s="8"/>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B102" s="6">
         <v>0.5</v>
       </c>
       <c r="C102" s="7" t="str">
-        <f>IFERROR(COMPLEX($B102,C$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="D102" s="7" t="str">
-        <f>IFERROR(COMPLEX($B102,D$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>0.5+j</v>
       </c>
       <c r="E102" s="7" t="str">
-        <f>IFERROR(COMPLEX($B102,E$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>0.5-j</v>
       </c>
       <c r="F102" s="7" t="str">
-        <f>IFERROR(COMPLEX($B102,F$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>0.5+5j</v>
       </c>
       <c r="G102" s="7" t="str">
-        <f>IFERROR(COMPLEX($B102,G$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>0.5-5j</v>
       </c>
       <c r="H102" s="7" t="str">
-        <f>IFERROR(COMPLEX($B102,H$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>0.5+0.5j</v>
       </c>
       <c r="I102" s="7" t="str">
-        <f>IFERROR(COMPLEX($B102,I$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>0.5-0.5j</v>
       </c>
       <c r="J102" s="8"/>
@@ -3576,36 +3569,36 @@
       <c r="L102" s="8"/>
       <c r="M102" s="8"/>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B103" s="6">
         <v>-0.5</v>
       </c>
       <c r="C103" s="7" t="str">
-        <f>IFERROR(COMPLEX($B103,C$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-0.5</v>
       </c>
       <c r="D103" s="7" t="str">
-        <f>IFERROR(COMPLEX($B103,D$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-0.5+j</v>
       </c>
       <c r="E103" s="7" t="str">
-        <f>IFERROR(COMPLEX($B103,E$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-0.5-j</v>
       </c>
       <c r="F103" s="7" t="str">
-        <f>IFERROR(COMPLEX($B103,F$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-0.5+5j</v>
       </c>
       <c r="G103" s="7" t="str">
-        <f>IFERROR(COMPLEX($B103,G$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-0.5-5j</v>
       </c>
       <c r="H103" s="7" t="str">
-        <f>IFERROR(COMPLEX($B103,H$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-0.5+0.5j</v>
       </c>
       <c r="I103" s="7" t="str">
-        <f>IFERROR(COMPLEX($B103,I$96,"j"),"N/A")</f>
+        <f t="shared" si="3"/>
         <v>-0.5-0.5j</v>
       </c>
       <c r="J103" s="8"/>
@@ -3613,7 +3606,7 @@
       <c r="L103" s="8"/>
       <c r="M103" s="8"/>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C104" s="9"/>
       <c r="D104" s="9"/>
       <c r="E104" s="9"/>
@@ -3626,8 +3619,8 @@
       <c r="L104" s="8"/>
       <c r="M104" s="8"/>
     </row>
-    <row r="105" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="18" t="s">
+    <row r="105" spans="2:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="17" t="s">
         <v>78</v>
       </c>
       <c r="C105" s="3"/>
@@ -3642,106 +3635,106 @@
       <c r="L105" s="3"/>
       <c r="M105" s="8"/>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B106" s="19" t="s">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B106" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C106" s="32">
+      <c r="C106" s="30">
         <f>C5</f>
         <v>0</v>
       </c>
-      <c r="D106" s="32">
+      <c r="D106" s="30">
         <f>C6</f>
         <v>1</v>
       </c>
-      <c r="E106" s="32">
+      <c r="E106" s="30">
         <f>C7</f>
         <v>-1</v>
       </c>
-      <c r="F106" s="32">
+      <c r="F106" s="30">
         <f>C8</f>
         <v>10</v>
       </c>
-      <c r="G106" s="32">
+      <c r="G106" s="30">
         <f>C9</f>
         <v>-10</v>
       </c>
-      <c r="H106" s="32">
+      <c r="H106" s="30">
         <f>C10</f>
         <v>511</v>
       </c>
-      <c r="I106" s="32">
+      <c r="I106" s="30">
         <f>C11</f>
         <v>-512</v>
       </c>
-      <c r="J106" s="32">
+      <c r="J106" s="30">
         <f>C12</f>
         <v>255</v>
       </c>
-      <c r="K106" s="32">
+      <c r="K106" s="30">
         <f>C13</f>
         <v>-255</v>
       </c>
-      <c r="L106" s="32">
+      <c r="L106" s="30">
         <f>C14</f>
         <v>42.5</v>
       </c>
-      <c r="M106" s="30">
+      <c r="M106" s="9">
         <f>$C$15</f>
         <v>-42.5</v>
       </c>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B107" s="21">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B107" s="20">
         <f>$C$5</f>
         <v>0</v>
       </c>
-      <c r="C107" s="26">
+      <c r="C107" s="25">
         <f>DELTA($C$5,$C$5)</f>
         <v>1</v>
       </c>
-      <c r="D107" s="26">
+      <c r="D107" s="25">
         <f>DELTA($C$5,$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E107" s="26">
+      <c r="E107" s="25">
         <f>DELTA($C$5,$C$7)</f>
         <v>0</v>
       </c>
-      <c r="F107" s="26">
+      <c r="F107" s="25">
         <f>DELTA($C$5,$C$8)</f>
         <v>0</v>
       </c>
-      <c r="G107" s="26">
+      <c r="G107" s="25">
         <f>DELTA($C$5,$C$9)</f>
         <v>0</v>
       </c>
-      <c r="H107" s="26">
+      <c r="H107" s="25">
         <f>DELTA($C$5,$C$10)</f>
         <v>0</v>
       </c>
-      <c r="I107" s="26">
+      <c r="I107" s="25">
         <f>DELTA($C$5,$C$11)</f>
         <v>0</v>
       </c>
-      <c r="J107" s="26">
+      <c r="J107" s="25">
         <f>DELTA($C$5,$C$12)</f>
         <v>0</v>
       </c>
-      <c r="K107" s="26">
+      <c r="K107" s="25">
         <f>DELTA($C$5,$C$13)</f>
         <v>0</v>
       </c>
-      <c r="L107" s="26">
+      <c r="L107" s="25">
         <f>DELTA($C$5,$C$14)</f>
         <v>0</v>
       </c>
-      <c r="M107" s="26">
+      <c r="M107" s="25">
         <f>DELTA($C$5,$C$15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B108" s="6">
         <f>$C$6</f>
         <v>1</v>
@@ -3791,7 +3784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B109" s="6">
         <f>$C$7</f>
         <v>-1</v>
@@ -3841,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B110" s="6">
         <f>$C$8</f>
         <v>10</v>
@@ -3891,7 +3884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B111" s="6">
         <f>$C$9</f>
         <v>-10</v>
@@ -3941,7 +3934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B112" s="6">
         <f>$C$10</f>
         <v>511</v>
@@ -3991,7 +3984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B113" s="6">
         <f>$C$11</f>
         <v>-512</v>
@@ -4041,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B114" s="6">
         <f>$C$12</f>
         <v>255</v>
@@ -4091,7 +4084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B115" s="6">
         <f>$C$13</f>
         <v>-255</v>
@@ -4141,7 +4134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B116" s="6">
         <f>$C$14</f>
         <v>42.5</v>
@@ -4191,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B117" s="6">
         <f>$C$15</f>
         <v>-42.5</v>
